--- a/AAII_Financials/Yearly/AG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AG_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -708,25 +708,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>787400</v>
+        <v>779500</v>
       </c>
       <c r="E8" s="3">
-        <v>856600</v>
+        <v>848000</v>
       </c>
       <c r="F8" s="3">
-        <v>801500</v>
+        <v>793500</v>
       </c>
       <c r="G8" s="3">
-        <v>499300</v>
+        <v>494300</v>
       </c>
       <c r="H8" s="3">
-        <v>499400</v>
+        <v>494400</v>
       </c>
       <c r="I8" s="3">
-        <v>412900</v>
+        <v>408800</v>
       </c>
       <c r="J8" s="3">
-        <v>346200</v>
+        <v>342700</v>
       </c>
       <c r="K8" s="3"/>
     </row>
@@ -735,25 +735,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>733700</v>
+        <v>726400</v>
       </c>
       <c r="E9" s="3">
-        <v>833600</v>
+        <v>825200</v>
       </c>
       <c r="F9" s="3">
-        <v>662400</v>
+        <v>655700</v>
       </c>
       <c r="G9" s="3">
-        <v>341300</v>
+        <v>337900</v>
       </c>
       <c r="H9" s="3">
-        <v>314500</v>
+        <v>311400</v>
       </c>
       <c r="I9" s="3">
-        <v>300700</v>
+        <v>297700</v>
       </c>
       <c r="J9" s="3">
-        <v>218500</v>
+        <v>216400</v>
       </c>
       <c r="K9" s="3"/>
     </row>
@@ -762,25 +762,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>53600</v>
+        <v>53100</v>
       </c>
       <c r="E10" s="3">
-        <v>23000</v>
+        <v>22800</v>
       </c>
       <c r="F10" s="3">
-        <v>139200</v>
+        <v>137800</v>
       </c>
       <c r="G10" s="3">
-        <v>158000</v>
+        <v>156500</v>
       </c>
       <c r="H10" s="3">
-        <v>184900</v>
+        <v>183000</v>
       </c>
       <c r="I10" s="3">
-        <v>112200</v>
+        <v>111100</v>
       </c>
       <c r="J10" s="3">
-        <v>127600</v>
+        <v>126400</v>
       </c>
       <c r="K10" s="3"/>
     </row>
@@ -856,25 +856,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>209600</v>
+        <v>207500</v>
       </c>
       <c r="E14" s="3">
         <v>-3600</v>
       </c>
       <c r="F14" s="3">
-        <v>12500</v>
+        <v>12400</v>
       </c>
       <c r="G14" s="3">
-        <v>13900</v>
+        <v>13700</v>
       </c>
       <c r="H14" s="3">
-        <v>84600</v>
+        <v>83800</v>
       </c>
       <c r="I14" s="3">
-        <v>280700</v>
+        <v>277900</v>
       </c>
       <c r="J14" s="3">
-        <v>89900</v>
+        <v>89000</v>
       </c>
       <c r="K14" s="3"/>
     </row>
@@ -883,7 +883,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="E15" s="3">
         <v>2200</v>
@@ -895,13 +895,13 @@
         <v>2600</v>
       </c>
       <c r="H15" s="3">
-        <v>92200</v>
+        <v>91300</v>
       </c>
       <c r="I15" s="3">
-        <v>129700</v>
+        <v>128400</v>
       </c>
       <c r="J15" s="3">
-        <v>107100</v>
+        <v>106100</v>
       </c>
       <c r="K15" s="3"/>
     </row>
@@ -920,25 +920,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1032700</v>
+        <v>1022400</v>
       </c>
       <c r="E17" s="3">
-        <v>910300</v>
+        <v>901200</v>
       </c>
       <c r="F17" s="3">
-        <v>743800</v>
+        <v>736400</v>
       </c>
       <c r="G17" s="3">
-        <v>443900</v>
+        <v>439500</v>
       </c>
       <c r="H17" s="3">
-        <v>543300</v>
+        <v>537900</v>
       </c>
       <c r="I17" s="3">
-        <v>755000</v>
+        <v>747400</v>
       </c>
       <c r="J17" s="3">
-        <v>443600</v>
+        <v>439200</v>
       </c>
       <c r="K17" s="3"/>
     </row>
@@ -947,25 +947,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-245300</v>
+        <v>-242900</v>
       </c>
       <c r="E18" s="3">
-        <v>-53800</v>
+        <v>-53200</v>
       </c>
       <c r="F18" s="3">
-        <v>57700</v>
+        <v>57100</v>
       </c>
       <c r="G18" s="3">
-        <v>55400</v>
+        <v>54800</v>
       </c>
       <c r="H18" s="3">
-        <v>-43900</v>
+        <v>-43500</v>
       </c>
       <c r="I18" s="3">
-        <v>-342000</v>
+        <v>-338600</v>
       </c>
       <c r="J18" s="3">
-        <v>-97400</v>
+        <v>-96400</v>
       </c>
       <c r="K18" s="3"/>
     </row>
@@ -990,7 +990,7 @@
         <v>-2600</v>
       </c>
       <c r="E20" s="3">
-        <v>-12700</v>
+        <v>-12600</v>
       </c>
       <c r="F20" s="3">
         <v>-5800</v>
@@ -1014,25 +1014,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-74300</v>
+        <v>-74100</v>
       </c>
       <c r="E21" s="3">
-        <v>122500</v>
+        <v>120800</v>
       </c>
       <c r="F21" s="3">
-        <v>214600</v>
+        <v>212000</v>
       </c>
       <c r="G21" s="3">
-        <v>134800</v>
+        <v>133200</v>
       </c>
       <c r="H21" s="3">
-        <v>55400</v>
+        <v>54600</v>
       </c>
       <c r="I21" s="3">
-        <v>-215900</v>
+        <v>-214200</v>
       </c>
       <c r="J21" s="3">
-        <v>7900</v>
+        <v>7600</v>
       </c>
       <c r="K21" s="3"/>
     </row>
@@ -1041,25 +1041,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>20900</v>
+        <v>20700</v>
       </c>
       <c r="E22" s="3">
-        <v>17800</v>
+        <v>17600</v>
       </c>
       <c r="F22" s="3">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="G22" s="3">
-        <v>16600</v>
+        <v>16400</v>
       </c>
       <c r="H22" s="3">
-        <v>16500</v>
+        <v>16300</v>
       </c>
       <c r="I22" s="3">
-        <v>15000</v>
+        <v>14800</v>
       </c>
       <c r="J22" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="K22" s="3"/>
     </row>
@@ -1068,25 +1068,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-268800</v>
+        <v>-266200</v>
       </c>
       <c r="E23" s="3">
-        <v>-84300</v>
+        <v>-83400</v>
       </c>
       <c r="F23" s="3">
-        <v>34600</v>
+        <v>34300</v>
       </c>
       <c r="G23" s="3">
-        <v>40800</v>
+        <v>40400</v>
       </c>
       <c r="H23" s="3">
-        <v>-53500</v>
+        <v>-53000</v>
       </c>
       <c r="I23" s="3">
-        <v>-361000</v>
+        <v>-357300</v>
       </c>
       <c r="J23" s="3">
-        <v>-103300</v>
+        <v>-102300</v>
       </c>
       <c r="K23" s="3"/>
     </row>
@@ -1095,25 +1095,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-83400</v>
+        <v>-82600</v>
       </c>
       <c r="E24" s="3">
-        <v>72600</v>
+        <v>71800</v>
       </c>
       <c r="F24" s="3">
-        <v>41400</v>
+        <v>41000</v>
       </c>
       <c r="G24" s="3">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="H24" s="3">
         <v>2000</v>
       </c>
       <c r="I24" s="3">
-        <v>-80800</v>
+        <v>-80000</v>
       </c>
       <c r="J24" s="3">
-        <v>-30200</v>
+        <v>-29900</v>
       </c>
       <c r="K24" s="3"/>
     </row>
@@ -1149,25 +1149,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-185400</v>
+        <v>-183500</v>
       </c>
       <c r="E26" s="3">
-        <v>-156800</v>
+        <v>-155200</v>
       </c>
       <c r="F26" s="3">
-        <v>-6800</v>
+        <v>-6700</v>
       </c>
       <c r="G26" s="3">
-        <v>31700</v>
+        <v>31400</v>
       </c>
       <c r="H26" s="3">
-        <v>-55500</v>
+        <v>-55000</v>
       </c>
       <c r="I26" s="3">
-        <v>-280200</v>
+        <v>-277400</v>
       </c>
       <c r="J26" s="3">
-        <v>-73100</v>
+        <v>-72400</v>
       </c>
       <c r="K26" s="3"/>
     </row>
@@ -1176,25 +1176,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-185400</v>
+        <v>-183500</v>
       </c>
       <c r="E27" s="3">
-        <v>-156800</v>
+        <v>-155200</v>
       </c>
       <c r="F27" s="3">
-        <v>-6800</v>
+        <v>-6700</v>
       </c>
       <c r="G27" s="3">
-        <v>31700</v>
+        <v>31400</v>
       </c>
       <c r="H27" s="3">
-        <v>-55500</v>
+        <v>-55000</v>
       </c>
       <c r="I27" s="3">
-        <v>-280200</v>
+        <v>-277400</v>
       </c>
       <c r="J27" s="3">
-        <v>-73100</v>
+        <v>-72400</v>
       </c>
       <c r="K27" s="3"/>
     </row>
@@ -1314,7 +1314,7 @@
         <v>2600</v>
       </c>
       <c r="E32" s="3">
-        <v>12700</v>
+        <v>12600</v>
       </c>
       <c r="F32" s="3">
         <v>5800</v>
@@ -1338,25 +1338,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-185400</v>
+        <v>-183500</v>
       </c>
       <c r="E33" s="3">
-        <v>-156800</v>
+        <v>-155200</v>
       </c>
       <c r="F33" s="3">
-        <v>-6800</v>
+        <v>-6700</v>
       </c>
       <c r="G33" s="3">
-        <v>31700</v>
+        <v>31400</v>
       </c>
       <c r="H33" s="3">
-        <v>-55500</v>
+        <v>-55000</v>
       </c>
       <c r="I33" s="3">
-        <v>-280200</v>
+        <v>-277400</v>
       </c>
       <c r="J33" s="3">
-        <v>-73100</v>
+        <v>-72400</v>
       </c>
       <c r="K33" s="3"/>
     </row>
@@ -1392,25 +1392,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-185400</v>
+        <v>-183500</v>
       </c>
       <c r="E35" s="3">
-        <v>-156800</v>
+        <v>-155200</v>
       </c>
       <c r="F35" s="3">
-        <v>-6800</v>
+        <v>-6700</v>
       </c>
       <c r="G35" s="3">
-        <v>31700</v>
+        <v>31400</v>
       </c>
       <c r="H35" s="3">
-        <v>-55500</v>
+        <v>-55000</v>
       </c>
       <c r="I35" s="3">
-        <v>-280200</v>
+        <v>-277400</v>
       </c>
       <c r="J35" s="3">
-        <v>-73100</v>
+        <v>-72400</v>
       </c>
       <c r="K35" s="3"/>
     </row>
@@ -1477,25 +1477,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>172300</v>
+        <v>170600</v>
       </c>
       <c r="E41" s="3">
-        <v>207800</v>
+        <v>205700</v>
       </c>
       <c r="F41" s="3">
-        <v>326500</v>
+        <v>323200</v>
       </c>
       <c r="G41" s="3">
-        <v>284200</v>
+        <v>281400</v>
       </c>
       <c r="H41" s="3">
-        <v>221300</v>
+        <v>219100</v>
       </c>
       <c r="I41" s="3">
-        <v>55400</v>
+        <v>54800</v>
       </c>
       <c r="J41" s="3">
-        <v>106200</v>
+        <v>105200</v>
       </c>
       <c r="K41" s="3"/>
     </row>
@@ -1504,25 +1504,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>85600</v>
+        <v>84700</v>
       </c>
       <c r="E42" s="3">
-        <v>47400</v>
+        <v>46900</v>
       </c>
       <c r="F42" s="3">
-        <v>36300</v>
+        <v>36000</v>
       </c>
       <c r="G42" s="3">
-        <v>93000</v>
+        <v>92100</v>
       </c>
       <c r="H42" s="3">
-        <v>19500</v>
+        <v>19400</v>
       </c>
       <c r="I42" s="3">
-        <v>31700</v>
+        <v>31400</v>
       </c>
       <c r="J42" s="3">
-        <v>71400</v>
+        <v>70700</v>
       </c>
       <c r="K42" s="3"/>
     </row>
@@ -1531,25 +1531,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>66800</v>
+        <v>66100</v>
       </c>
       <c r="E43" s="3">
-        <v>56600</v>
+        <v>56000</v>
       </c>
       <c r="F43" s="3">
-        <v>74500</v>
+        <v>73700</v>
       </c>
       <c r="G43" s="3">
-        <v>63000</v>
+        <v>62400</v>
       </c>
       <c r="H43" s="3">
-        <v>46600</v>
+        <v>46100</v>
       </c>
       <c r="I43" s="3">
-        <v>90900</v>
+        <v>90000</v>
       </c>
       <c r="J43" s="3">
-        <v>28600</v>
+        <v>28300</v>
       </c>
       <c r="K43" s="3"/>
     </row>
@@ -1558,25 +1558,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>87400</v>
+        <v>86500</v>
       </c>
       <c r="E44" s="3">
-        <v>88900</v>
+        <v>88000</v>
       </c>
       <c r="F44" s="3">
-        <v>83200</v>
+        <v>82300</v>
       </c>
       <c r="G44" s="3">
-        <v>44600</v>
+        <v>44200</v>
       </c>
       <c r="H44" s="3">
-        <v>41900</v>
+        <v>41500</v>
       </c>
       <c r="I44" s="3">
-        <v>44600</v>
+        <v>44100</v>
       </c>
       <c r="J44" s="3">
-        <v>25900</v>
+        <v>25600</v>
       </c>
       <c r="K44" s="3"/>
     </row>
@@ -1585,13 +1585,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>12000</v>
+        <v>11800</v>
       </c>
       <c r="E45" s="3">
-        <v>107500</v>
+        <v>106400</v>
       </c>
       <c r="F45" s="3">
-        <v>24600</v>
+        <v>24300</v>
       </c>
       <c r="G45" s="3">
         <v>3700</v>
@@ -1600,7 +1600,7 @@
         <v>4100</v>
       </c>
       <c r="I45" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="J45" s="3">
         <v>2000</v>
@@ -1612,25 +1612,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>424100</v>
+        <v>419900</v>
       </c>
       <c r="E46" s="3">
-        <v>508100</v>
+        <v>503000</v>
       </c>
       <c r="F46" s="3">
-        <v>545000</v>
+        <v>539600</v>
       </c>
       <c r="G46" s="3">
-        <v>488600</v>
+        <v>483700</v>
       </c>
       <c r="H46" s="3">
-        <v>333400</v>
+        <v>330100</v>
       </c>
       <c r="I46" s="3">
-        <v>228200</v>
+        <v>225900</v>
       </c>
       <c r="J46" s="3">
-        <v>234200</v>
+        <v>231800</v>
       </c>
       <c r="K46" s="3"/>
     </row>
@@ -1639,22 +1639,22 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>19400</v>
+        <v>19200</v>
       </c>
       <c r="E47" s="3">
-        <v>17000</v>
+        <v>16800</v>
       </c>
       <c r="F47" s="3">
         <v>800</v>
       </c>
       <c r="G47" s="3">
-        <v>21000</v>
+        <v>20800</v>
       </c>
       <c r="H47" s="3">
-        <v>26800</v>
+        <v>26600</v>
       </c>
       <c r="I47" s="3">
-        <v>25700</v>
+        <v>25500</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -1666,25 +1666,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1965600</v>
+        <v>1945900</v>
       </c>
       <c r="E48" s="3">
-        <v>2112000</v>
+        <v>2090900</v>
       </c>
       <c r="F48" s="3">
-        <v>2095300</v>
+        <v>2074400</v>
       </c>
       <c r="G48" s="3">
-        <v>1073400</v>
+        <v>1062700</v>
       </c>
       <c r="H48" s="3">
-        <v>977100</v>
+        <v>967300</v>
       </c>
       <c r="I48" s="3">
-        <v>942300</v>
+        <v>932900</v>
       </c>
       <c r="J48" s="3">
-        <v>776900</v>
+        <v>769200</v>
       </c>
       <c r="K48" s="3"/>
     </row>
@@ -1774,25 +1774,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>302900</v>
+        <v>299900</v>
       </c>
       <c r="E52" s="3">
-        <v>258300</v>
+        <v>255700</v>
       </c>
       <c r="F52" s="3">
-        <v>274700</v>
+        <v>272000</v>
       </c>
       <c r="G52" s="3">
-        <v>115100</v>
+        <v>114000</v>
       </c>
       <c r="H52" s="3">
-        <v>73200</v>
+        <v>72400</v>
       </c>
       <c r="I52" s="3">
-        <v>74700</v>
+        <v>73900</v>
       </c>
       <c r="J52" s="3">
-        <v>61200</v>
+        <v>60600</v>
       </c>
       <c r="K52" s="3"/>
     </row>
@@ -1828,25 +1828,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2712000</v>
+        <v>2684900</v>
       </c>
       <c r="E54" s="3">
-        <v>2895400</v>
+        <v>2866400</v>
       </c>
       <c r="F54" s="3">
-        <v>2915900</v>
+        <v>2886800</v>
       </c>
       <c r="G54" s="3">
-        <v>1698100</v>
+        <v>1681200</v>
       </c>
       <c r="H54" s="3">
-        <v>1410500</v>
+        <v>1396400</v>
       </c>
       <c r="I54" s="3">
-        <v>1270800</v>
+        <v>1258100</v>
       </c>
       <c r="J54" s="3">
-        <v>1072300</v>
+        <v>1061600</v>
       </c>
       <c r="K54" s="3"/>
     </row>
@@ -1881,25 +1881,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>43700</v>
+        <v>43300</v>
       </c>
       <c r="E57" s="3">
-        <v>56000</v>
+        <v>55400</v>
       </c>
       <c r="F57" s="3">
-        <v>57400</v>
+        <v>56800</v>
       </c>
       <c r="G57" s="3">
-        <v>42900</v>
+        <v>42500</v>
       </c>
       <c r="H57" s="3">
-        <v>32900</v>
+        <v>32600</v>
       </c>
       <c r="I57" s="3">
-        <v>36300</v>
+        <v>35900</v>
       </c>
       <c r="J57" s="3">
-        <v>25100</v>
+        <v>24800</v>
       </c>
       <c r="K57" s="3"/>
     </row>
@@ -1908,25 +1908,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>25000</v>
+        <v>24700</v>
       </c>
       <c r="E58" s="3">
-        <v>19700</v>
+        <v>19500</v>
       </c>
       <c r="F58" s="3">
-        <v>16400</v>
+        <v>16200</v>
       </c>
       <c r="G58" s="3">
-        <v>22400</v>
+        <v>22200</v>
       </c>
       <c r="H58" s="3">
-        <v>11100</v>
+        <v>11000</v>
       </c>
       <c r="I58" s="3">
         <v>5700</v>
       </c>
       <c r="J58" s="3">
-        <v>22800</v>
+        <v>22600</v>
       </c>
       <c r="K58" s="3"/>
     </row>
@@ -1935,25 +1935,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>96200</v>
+        <v>95200</v>
       </c>
       <c r="E59" s="3">
-        <v>154000</v>
+        <v>152500</v>
       </c>
       <c r="F59" s="3">
-        <v>163400</v>
+        <v>161700</v>
       </c>
       <c r="G59" s="3">
-        <v>74100</v>
+        <v>73400</v>
       </c>
       <c r="H59" s="3">
-        <v>54600</v>
+        <v>54000</v>
       </c>
       <c r="I59" s="3">
-        <v>37800</v>
+        <v>37400</v>
       </c>
       <c r="J59" s="3">
-        <v>26700</v>
+        <v>26500</v>
       </c>
       <c r="K59" s="3"/>
     </row>
@@ -1962,25 +1962,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>164900</v>
+        <v>163200</v>
       </c>
       <c r="E60" s="3">
-        <v>229700</v>
+        <v>227400</v>
       </c>
       <c r="F60" s="3">
-        <v>237100</v>
+        <v>234800</v>
       </c>
       <c r="G60" s="3">
-        <v>139500</v>
+        <v>138100</v>
       </c>
       <c r="H60" s="3">
-        <v>98600</v>
+        <v>97600</v>
       </c>
       <c r="I60" s="3">
-        <v>79800</v>
+        <v>79000</v>
       </c>
       <c r="J60" s="3">
-        <v>74600</v>
+        <v>73900</v>
       </c>
       <c r="K60" s="3"/>
     </row>
@@ -1989,25 +1989,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>327000</v>
+        <v>323700</v>
       </c>
       <c r="E61" s="3">
-        <v>320500</v>
+        <v>317300</v>
       </c>
       <c r="F61" s="3">
-        <v>287000</v>
+        <v>284100</v>
       </c>
       <c r="G61" s="3">
-        <v>215400</v>
+        <v>213200</v>
       </c>
       <c r="H61" s="3">
-        <v>232800</v>
+        <v>230500</v>
       </c>
       <c r="I61" s="3">
-        <v>207400</v>
+        <v>205400</v>
       </c>
       <c r="J61" s="3">
-        <v>33600</v>
+        <v>33200</v>
       </c>
       <c r="K61" s="3"/>
     </row>
@@ -2016,25 +2016,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>356500</v>
+        <v>352900</v>
       </c>
       <c r="E62" s="3">
-        <v>408600</v>
+        <v>404500</v>
       </c>
       <c r="F62" s="3">
-        <v>455600</v>
+        <v>451100</v>
       </c>
       <c r="G62" s="3">
-        <v>176600</v>
+        <v>174800</v>
       </c>
       <c r="H62" s="3">
-        <v>170300</v>
+        <v>168600</v>
       </c>
       <c r="I62" s="3">
-        <v>167700</v>
+        <v>166000</v>
       </c>
       <c r="J62" s="3">
-        <v>164800</v>
+        <v>163200</v>
       </c>
       <c r="K62" s="3"/>
     </row>
@@ -2124,25 +2124,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>848300</v>
+        <v>839900</v>
       </c>
       <c r="E66" s="3">
-        <v>958800</v>
+        <v>949200</v>
       </c>
       <c r="F66" s="3">
-        <v>979800</v>
+        <v>970000</v>
       </c>
       <c r="G66" s="3">
-        <v>531400</v>
+        <v>526100</v>
       </c>
       <c r="H66" s="3">
-        <v>501700</v>
+        <v>496700</v>
       </c>
       <c r="I66" s="3">
-        <v>454900</v>
+        <v>450400</v>
       </c>
       <c r="J66" s="3">
-        <v>273000</v>
+        <v>270300</v>
       </c>
       <c r="K66" s="3"/>
     </row>
@@ -2272,25 +2272,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-673200</v>
+        <v>-666400</v>
       </c>
       <c r="E72" s="3">
-        <v>-491200</v>
+        <v>-486300</v>
       </c>
       <c r="F72" s="3">
-        <v>-338100</v>
+        <v>-334700</v>
       </c>
       <c r="G72" s="3">
-        <v>-361500</v>
+        <v>-357900</v>
       </c>
       <c r="H72" s="3">
-        <v>-394500</v>
+        <v>-390600</v>
       </c>
       <c r="I72" s="3">
-        <v>-342200</v>
+        <v>-338800</v>
       </c>
       <c r="J72" s="3">
-        <v>-70200</v>
+        <v>-69500</v>
       </c>
       <c r="K72" s="3"/>
     </row>
@@ -2380,25 +2380,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1863600</v>
+        <v>1845000</v>
       </c>
       <c r="E76" s="3">
-        <v>1936600</v>
+        <v>1917200</v>
       </c>
       <c r="F76" s="3">
-        <v>1936100</v>
+        <v>1916800</v>
       </c>
       <c r="G76" s="3">
-        <v>1166700</v>
+        <v>1155000</v>
       </c>
       <c r="H76" s="3">
-        <v>908800</v>
+        <v>899800</v>
       </c>
       <c r="I76" s="3">
-        <v>815900</v>
+        <v>807700</v>
       </c>
       <c r="J76" s="3">
-        <v>799300</v>
+        <v>791300</v>
       </c>
       <c r="K76" s="3"/>
     </row>
@@ -2466,25 +2466,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-185400</v>
+        <v>-183500</v>
       </c>
       <c r="E81" s="3">
-        <v>-156800</v>
+        <v>-155200</v>
       </c>
       <c r="F81" s="3">
-        <v>-6800</v>
+        <v>-6700</v>
       </c>
       <c r="G81" s="3">
-        <v>31700</v>
+        <v>31400</v>
       </c>
       <c r="H81" s="3">
-        <v>-55500</v>
+        <v>-55000</v>
       </c>
       <c r="I81" s="3">
-        <v>-280200</v>
+        <v>-277400</v>
       </c>
       <c r="J81" s="3">
-        <v>-73100</v>
+        <v>-72400</v>
       </c>
       <c r="K81" s="3"/>
     </row>
@@ -2506,25 +2506,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>173100</v>
+        <v>171400</v>
       </c>
       <c r="E83" s="3">
-        <v>188600</v>
+        <v>186700</v>
       </c>
       <c r="F83" s="3">
-        <v>162300</v>
+        <v>160700</v>
       </c>
       <c r="G83" s="3">
-        <v>77200</v>
+        <v>76500</v>
       </c>
       <c r="H83" s="3">
-        <v>92200</v>
+        <v>91300</v>
       </c>
       <c r="I83" s="3">
-        <v>129700</v>
+        <v>128400</v>
       </c>
       <c r="J83" s="3">
-        <v>107100</v>
+        <v>106100</v>
       </c>
       <c r="K83" s="3"/>
     </row>
@@ -2668,25 +2668,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>83500</v>
+        <v>82600</v>
       </c>
       <c r="E89" s="3">
-        <v>18900</v>
+        <v>18700</v>
       </c>
       <c r="F89" s="3">
-        <v>94300</v>
+        <v>93400</v>
       </c>
       <c r="G89" s="3">
-        <v>109400</v>
+        <v>108300</v>
       </c>
       <c r="H89" s="3">
-        <v>192100</v>
+        <v>190200</v>
       </c>
       <c r="I89" s="3">
-        <v>45600</v>
+        <v>45200</v>
       </c>
       <c r="J89" s="3">
-        <v>96700</v>
+        <v>95700</v>
       </c>
       <c r="K89" s="3"/>
     </row>
@@ -2708,25 +2708,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200300</v>
+        <v>-198300</v>
       </c>
       <c r="E91" s="3">
-        <v>-298700</v>
+        <v>-295700</v>
       </c>
       <c r="F91" s="3">
-        <v>-259300</v>
+        <v>-256700</v>
       </c>
       <c r="G91" s="3">
-        <v>-157100</v>
+        <v>-155500</v>
       </c>
       <c r="H91" s="3">
-        <v>-162800</v>
+        <v>-161100</v>
       </c>
       <c r="I91" s="3">
-        <v>-152700</v>
+        <v>-151200</v>
       </c>
       <c r="J91" s="3">
-        <v>-103600</v>
+        <v>-102600</v>
       </c>
       <c r="K91" s="3"/>
     </row>
@@ -2789,25 +2789,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-211300</v>
+        <v>-209200</v>
       </c>
       <c r="E94" s="3">
-        <v>-293400</v>
+        <v>-290400</v>
       </c>
       <c r="F94" s="3">
-        <v>-248000</v>
+        <v>-245600</v>
       </c>
       <c r="G94" s="3">
-        <v>-174400</v>
+        <v>-172700</v>
       </c>
       <c r="H94" s="3">
-        <v>-160500</v>
+        <v>-158900</v>
       </c>
       <c r="I94" s="3">
-        <v>-160600</v>
+        <v>-159000</v>
       </c>
       <c r="J94" s="3">
-        <v>-104200</v>
+        <v>-103100</v>
       </c>
       <c r="K94" s="3"/>
     </row>
@@ -2829,13 +2829,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8100</v>
+        <v>-8000</v>
       </c>
       <c r="E96" s="3">
-        <v>-9400</v>
+        <v>-9300</v>
       </c>
       <c r="F96" s="3">
-        <v>-5400</v>
+        <v>-5300</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -2937,25 +2937,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>88700</v>
+        <v>87800</v>
       </c>
       <c r="E100" s="3">
-        <v>156300</v>
+        <v>154700</v>
       </c>
       <c r="F100" s="3">
-        <v>153400</v>
+        <v>151900</v>
       </c>
       <c r="G100" s="3">
-        <v>160000</v>
+        <v>158400</v>
       </c>
       <c r="H100" s="3">
-        <v>120300</v>
+        <v>119100</v>
       </c>
       <c r="I100" s="3">
-        <v>34900</v>
+        <v>34600</v>
       </c>
       <c r="J100" s="3">
-        <v>-11900</v>
+        <v>-11800</v>
       </c>
       <c r="K100" s="3"/>
     </row>
@@ -2964,7 +2964,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="E101" s="3">
         <v>-500</v>
@@ -2991,25 +2991,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-35500</v>
+        <v>-35100</v>
       </c>
       <c r="E102" s="3">
-        <v>-118700</v>
+        <v>-117500</v>
       </c>
       <c r="F102" s="3">
         <v>-900</v>
       </c>
       <c r="G102" s="3">
-        <v>95500</v>
+        <v>94500</v>
       </c>
       <c r="H102" s="3">
-        <v>153700</v>
+        <v>152100</v>
       </c>
       <c r="I102" s="3">
-        <v>-83900</v>
+        <v>-83000</v>
       </c>
       <c r="J102" s="3">
-        <v>-15000</v>
+        <v>-14800</v>
       </c>
       <c r="K102" s="3"/>
     </row>

--- a/AAII_Financials/Yearly/AG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>AG</t>
   </si>
@@ -708,25 +708,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>779500</v>
+        <v>573800</v>
       </c>
       <c r="E8" s="3">
-        <v>848000</v>
+        <v>624200</v>
       </c>
       <c r="F8" s="3">
-        <v>793500</v>
+        <v>584100</v>
       </c>
       <c r="G8" s="3">
-        <v>494300</v>
+        <v>363900</v>
       </c>
       <c r="H8" s="3">
-        <v>494400</v>
+        <v>363900</v>
       </c>
       <c r="I8" s="3">
-        <v>408800</v>
+        <v>300900</v>
       </c>
       <c r="J8" s="3">
-        <v>342700</v>
+        <v>252300</v>
       </c>
       <c r="K8" s="3"/>
     </row>
@@ -735,25 +735,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>726400</v>
+        <v>432100</v>
       </c>
       <c r="E9" s="3">
-        <v>825200</v>
+        <v>483600</v>
       </c>
       <c r="F9" s="3">
-        <v>655700</v>
+        <v>378100</v>
       </c>
       <c r="G9" s="3">
-        <v>337900</v>
+        <v>218800</v>
       </c>
       <c r="H9" s="3">
-        <v>311400</v>
+        <v>236500</v>
       </c>
       <c r="I9" s="3">
-        <v>297700</v>
+        <v>221300</v>
       </c>
       <c r="J9" s="3">
-        <v>216400</v>
+        <v>159300</v>
       </c>
       <c r="K9" s="3"/>
     </row>
@@ -762,25 +762,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>53100</v>
+        <v>141700</v>
       </c>
       <c r="E10" s="3">
-        <v>22800</v>
+        <v>140600</v>
       </c>
       <c r="F10" s="3">
-        <v>137800</v>
+        <v>206000</v>
       </c>
       <c r="G10" s="3">
-        <v>156500</v>
+        <v>145000</v>
       </c>
       <c r="H10" s="3">
-        <v>183000</v>
+        <v>127500</v>
       </c>
       <c r="I10" s="3">
-        <v>111100</v>
+        <v>79700</v>
       </c>
       <c r="J10" s="3">
-        <v>126400</v>
+        <v>93000</v>
       </c>
       <c r="K10" s="3"/>
     </row>
@@ -856,25 +856,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>207500</v>
+        <v>61900</v>
       </c>
       <c r="E14" s="3">
-        <v>-3600</v>
+        <v>-3100</v>
       </c>
       <c r="F14" s="3">
-        <v>12400</v>
+        <v>11200</v>
       </c>
       <c r="G14" s="3">
-        <v>13700</v>
+        <v>8900</v>
       </c>
       <c r="H14" s="3">
-        <v>83800</v>
+        <v>37800</v>
       </c>
       <c r="I14" s="3">
-        <v>277900</v>
+        <v>60300</v>
       </c>
       <c r="J14" s="3">
-        <v>89000</v>
+        <v>24400</v>
       </c>
       <c r="K14" s="3"/>
     </row>
@@ -883,25 +883,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2000</v>
+        <v>220200</v>
       </c>
       <c r="E15" s="3">
-        <v>2200</v>
+        <v>135800</v>
       </c>
       <c r="F15" s="3">
-        <v>2300</v>
+        <v>116600</v>
       </c>
       <c r="G15" s="3">
-        <v>2600</v>
+        <v>54400</v>
       </c>
       <c r="H15" s="3">
-        <v>91300</v>
+        <v>89200</v>
       </c>
       <c r="I15" s="3">
-        <v>128400</v>
+        <v>242700</v>
       </c>
       <c r="J15" s="3">
-        <v>106100</v>
+        <v>120700</v>
       </c>
       <c r="K15" s="3"/>
     </row>
@@ -920,25 +920,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1022400</v>
+        <v>712500</v>
       </c>
       <c r="E17" s="3">
-        <v>901200</v>
+        <v>675800</v>
       </c>
       <c r="F17" s="3">
-        <v>736400</v>
+        <v>537300</v>
       </c>
       <c r="G17" s="3">
-        <v>439500</v>
+        <v>308700</v>
       </c>
       <c r="H17" s="3">
-        <v>537900</v>
+        <v>363300</v>
       </c>
       <c r="I17" s="3">
-        <v>747400</v>
+        <v>494200</v>
       </c>
       <c r="J17" s="3">
-        <v>439200</v>
+        <v>306700</v>
       </c>
       <c r="K17" s="3"/>
     </row>
@@ -947,25 +947,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-242900</v>
+        <v>-138700</v>
       </c>
       <c r="E18" s="3">
-        <v>-53200</v>
+        <v>-51600</v>
       </c>
       <c r="F18" s="3">
-        <v>57100</v>
+        <v>46800</v>
       </c>
       <c r="G18" s="3">
-        <v>54800</v>
+        <v>55200</v>
       </c>
       <c r="H18" s="3">
-        <v>-43500</v>
+        <v>700</v>
       </c>
       <c r="I18" s="3">
-        <v>-338600</v>
+        <v>-193300</v>
       </c>
       <c r="J18" s="3">
-        <v>-96400</v>
+        <v>-54400</v>
       </c>
       <c r="K18" s="3"/>
     </row>
@@ -987,25 +987,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2600</v>
+        <v>-13500</v>
       </c>
       <c r="E20" s="3">
-        <v>-12600</v>
+        <v>2300</v>
       </c>
       <c r="F20" s="3">
-        <v>-5800</v>
+        <v>-1100</v>
       </c>
       <c r="G20" s="3">
-        <v>2000</v>
+        <v>7600</v>
       </c>
       <c r="H20" s="3">
-        <v>6800</v>
+        <v>-3800</v>
       </c>
       <c r="I20" s="3">
-        <v>-3900</v>
+        <v>2500</v>
       </c>
       <c r="J20" s="3">
-        <v>-2000</v>
+        <v>-3800</v>
       </c>
       <c r="K20" s="3"/>
     </row>
@@ -1014,25 +1014,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-74100</v>
+        <v>94900</v>
       </c>
       <c r="E21" s="3">
-        <v>120800</v>
+        <v>81900</v>
       </c>
       <c r="F21" s="3">
-        <v>212000</v>
+        <v>164500</v>
       </c>
       <c r="G21" s="3">
-        <v>133200</v>
+        <v>101900</v>
       </c>
       <c r="H21" s="3">
-        <v>54600</v>
+        <v>93700</v>
       </c>
       <c r="I21" s="3">
-        <v>-214200</v>
+        <v>46900</v>
       </c>
       <c r="J21" s="3">
-        <v>7600</v>
+        <v>70100</v>
       </c>
       <c r="K21" s="3"/>
     </row>
@@ -1041,25 +1041,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>20700</v>
+        <v>15200</v>
       </c>
       <c r="E22" s="3">
-        <v>17600</v>
+        <v>12900</v>
       </c>
       <c r="F22" s="3">
-        <v>17100</v>
+        <v>12600</v>
       </c>
       <c r="G22" s="3">
-        <v>16400</v>
+        <v>12100</v>
       </c>
       <c r="H22" s="3">
-        <v>16300</v>
+        <v>12000</v>
       </c>
       <c r="I22" s="3">
-        <v>14800</v>
+        <v>10900</v>
       </c>
       <c r="J22" s="3">
-        <v>3800</v>
+        <v>2800</v>
       </c>
       <c r="K22" s="3"/>
     </row>
@@ -1068,25 +1068,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-266200</v>
+        <v>-195900</v>
       </c>
       <c r="E23" s="3">
-        <v>-83400</v>
+        <v>-61400</v>
       </c>
       <c r="F23" s="3">
-        <v>34300</v>
+        <v>25300</v>
       </c>
       <c r="G23" s="3">
-        <v>40400</v>
+        <v>29700</v>
       </c>
       <c r="H23" s="3">
-        <v>-53000</v>
+        <v>-39000</v>
       </c>
       <c r="I23" s="3">
-        <v>-357300</v>
+        <v>-263000</v>
       </c>
       <c r="J23" s="3">
-        <v>-102300</v>
+        <v>-75300</v>
       </c>
       <c r="K23" s="3"/>
     </row>
@@ -1095,25 +1095,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-82600</v>
+        <v>-60800</v>
       </c>
       <c r="E24" s="3">
-        <v>71800</v>
+        <v>52900</v>
       </c>
       <c r="F24" s="3">
-        <v>41000</v>
+        <v>30200</v>
       </c>
       <c r="G24" s="3">
-        <v>9000</v>
+        <v>6600</v>
       </c>
       <c r="H24" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I24" s="3">
-        <v>-80000</v>
+        <v>-58900</v>
       </c>
       <c r="J24" s="3">
-        <v>-29900</v>
+        <v>-22000</v>
       </c>
       <c r="K24" s="3"/>
     </row>
@@ -1149,25 +1149,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-183500</v>
+        <v>-135100</v>
       </c>
       <c r="E26" s="3">
-        <v>-155200</v>
+        <v>-114300</v>
       </c>
       <c r="F26" s="3">
-        <v>-6700</v>
+        <v>-4900</v>
       </c>
       <c r="G26" s="3">
-        <v>31400</v>
+        <v>23100</v>
       </c>
       <c r="H26" s="3">
-        <v>-55000</v>
+        <v>-40500</v>
       </c>
       <c r="I26" s="3">
-        <v>-277400</v>
+        <v>-204200</v>
       </c>
       <c r="J26" s="3">
-        <v>-72400</v>
+        <v>-53300</v>
       </c>
       <c r="K26" s="3"/>
     </row>
@@ -1176,25 +1176,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-183500</v>
+        <v>-135100</v>
       </c>
       <c r="E27" s="3">
-        <v>-155200</v>
+        <v>-114300</v>
       </c>
       <c r="F27" s="3">
-        <v>-6700</v>
+        <v>-4900</v>
       </c>
       <c r="G27" s="3">
-        <v>31400</v>
+        <v>23100</v>
       </c>
       <c r="H27" s="3">
-        <v>-55000</v>
+        <v>-40500</v>
       </c>
       <c r="I27" s="3">
-        <v>-277400</v>
+        <v>-204200</v>
       </c>
       <c r="J27" s="3">
-        <v>-72400</v>
+        <v>-53300</v>
       </c>
       <c r="K27" s="3"/>
     </row>
@@ -1311,25 +1311,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2600</v>
+        <v>13500</v>
       </c>
       <c r="E32" s="3">
-        <v>12600</v>
+        <v>-2300</v>
       </c>
       <c r="F32" s="3">
-        <v>5800</v>
+        <v>1100</v>
       </c>
       <c r="G32" s="3">
-        <v>-2000</v>
+        <v>-7600</v>
       </c>
       <c r="H32" s="3">
-        <v>-6800</v>
+        <v>3800</v>
       </c>
       <c r="I32" s="3">
-        <v>3900</v>
+        <v>-2500</v>
       </c>
       <c r="J32" s="3">
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="K32" s="3"/>
     </row>
@@ -1338,25 +1338,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-183500</v>
+        <v>-135100</v>
       </c>
       <c r="E33" s="3">
-        <v>-155200</v>
+        <v>-114300</v>
       </c>
       <c r="F33" s="3">
-        <v>-6700</v>
+        <v>-4900</v>
       </c>
       <c r="G33" s="3">
-        <v>31400</v>
+        <v>23100</v>
       </c>
       <c r="H33" s="3">
-        <v>-55000</v>
+        <v>-40500</v>
       </c>
       <c r="I33" s="3">
-        <v>-277400</v>
+        <v>-204200</v>
       </c>
       <c r="J33" s="3">
-        <v>-72400</v>
+        <v>-53300</v>
       </c>
       <c r="K33" s="3"/>
     </row>
@@ -1392,25 +1392,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-183500</v>
+        <v>-135100</v>
       </c>
       <c r="E35" s="3">
-        <v>-155200</v>
+        <v>-114300</v>
       </c>
       <c r="F35" s="3">
-        <v>-6700</v>
+        <v>-4900</v>
       </c>
       <c r="G35" s="3">
-        <v>31400</v>
+        <v>23100</v>
       </c>
       <c r="H35" s="3">
-        <v>-55000</v>
+        <v>-40500</v>
       </c>
       <c r="I35" s="3">
-        <v>-277400</v>
+        <v>-204200</v>
       </c>
       <c r="J35" s="3">
-        <v>-72400</v>
+        <v>-53300</v>
       </c>
       <c r="K35" s="3"/>
     </row>
@@ -1477,25 +1477,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>170600</v>
+        <v>125600</v>
       </c>
       <c r="E41" s="3">
-        <v>205700</v>
+        <v>151400</v>
       </c>
       <c r="F41" s="3">
-        <v>323200</v>
+        <v>237900</v>
       </c>
       <c r="G41" s="3">
-        <v>281400</v>
+        <v>238600</v>
       </c>
       <c r="H41" s="3">
-        <v>219100</v>
+        <v>169000</v>
       </c>
       <c r="I41" s="3">
-        <v>54800</v>
+        <v>57000</v>
       </c>
       <c r="J41" s="3">
-        <v>105200</v>
+        <v>118100</v>
       </c>
       <c r="K41" s="3"/>
     </row>
@@ -1504,25 +1504,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>84700</v>
+        <v>62400</v>
       </c>
       <c r="E42" s="3">
-        <v>46900</v>
+        <v>34500</v>
       </c>
       <c r="F42" s="3">
-        <v>36000</v>
+        <v>26500</v>
       </c>
       <c r="G42" s="3">
-        <v>92100</v>
+        <v>36300</v>
       </c>
       <c r="H42" s="3">
-        <v>19400</v>
+        <v>6500</v>
       </c>
       <c r="I42" s="3">
-        <v>31400</v>
+        <v>6400</v>
       </c>
       <c r="J42" s="3">
-        <v>70700</v>
+        <v>11300</v>
       </c>
       <c r="K42" s="3"/>
     </row>
@@ -1531,25 +1531,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>66100</v>
+        <v>48700</v>
       </c>
       <c r="E43" s="3">
-        <v>56000</v>
+        <v>41200</v>
       </c>
       <c r="F43" s="3">
-        <v>73700</v>
+        <v>54300</v>
       </c>
       <c r="G43" s="3">
-        <v>62400</v>
+        <v>45900</v>
       </c>
       <c r="H43" s="3">
-        <v>46100</v>
+        <v>33900</v>
       </c>
       <c r="I43" s="3">
-        <v>90000</v>
+        <v>66200</v>
       </c>
       <c r="J43" s="3">
-        <v>28300</v>
+        <v>20900</v>
       </c>
       <c r="K43" s="3"/>
     </row>
@@ -1558,25 +1558,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>86500</v>
+        <v>63700</v>
       </c>
       <c r="E44" s="3">
-        <v>88000</v>
+        <v>64800</v>
       </c>
       <c r="F44" s="3">
-        <v>82300</v>
+        <v>60600</v>
       </c>
       <c r="G44" s="3">
-        <v>44200</v>
+        <v>32500</v>
       </c>
       <c r="H44" s="3">
-        <v>41500</v>
+        <v>30500</v>
       </c>
       <c r="I44" s="3">
-        <v>44100</v>
+        <v>32500</v>
       </c>
       <c r="J44" s="3">
-        <v>25600</v>
+        <v>18900</v>
       </c>
       <c r="K44" s="3"/>
     </row>
@@ -1584,26 +1584,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>11800</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>106400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>24300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3700</v>
+        <v>72700</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H45" s="3">
-        <v>4100</v>
+        <v>1000</v>
       </c>
       <c r="I45" s="3">
-        <v>5600</v>
-      </c>
-      <c r="J45" s="3">
         <v>2000</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3"/>
     </row>
@@ -1612,25 +1612,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>419900</v>
+        <v>309100</v>
       </c>
       <c r="E46" s="3">
-        <v>503000</v>
+        <v>370300</v>
       </c>
       <c r="F46" s="3">
-        <v>539600</v>
+        <v>397200</v>
       </c>
       <c r="G46" s="3">
-        <v>483700</v>
+        <v>356000</v>
       </c>
       <c r="H46" s="3">
-        <v>330100</v>
+        <v>243000</v>
       </c>
       <c r="I46" s="3">
-        <v>225900</v>
+        <v>166300</v>
       </c>
       <c r="J46" s="3">
-        <v>231800</v>
+        <v>170700</v>
       </c>
       <c r="K46" s="3"/>
     </row>
@@ -1638,23 +1638,23 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>19200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>16800</v>
-      </c>
-      <c r="F47" s="3">
-        <v>800</v>
-      </c>
-      <c r="G47" s="3">
-        <v>20800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>26600</v>
-      </c>
-      <c r="I47" s="3">
-        <v>25500</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -1666,25 +1666,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1945900</v>
+        <v>1432400</v>
       </c>
       <c r="E48" s="3">
-        <v>2090900</v>
+        <v>1539100</v>
       </c>
       <c r="F48" s="3">
-        <v>2074400</v>
+        <v>1527000</v>
       </c>
       <c r="G48" s="3">
-        <v>1062700</v>
+        <v>782300</v>
       </c>
       <c r="H48" s="3">
-        <v>967300</v>
+        <v>712100</v>
       </c>
       <c r="I48" s="3">
-        <v>932900</v>
+        <v>686700</v>
       </c>
       <c r="J48" s="3">
-        <v>769200</v>
+        <v>566200</v>
       </c>
       <c r="K48" s="3"/>
     </row>
@@ -1774,25 +1774,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>299900</v>
+        <v>146200</v>
       </c>
       <c r="E52" s="3">
-        <v>255700</v>
+        <v>143600</v>
       </c>
       <c r="F52" s="3">
-        <v>272000</v>
+        <v>126500</v>
       </c>
       <c r="G52" s="3">
-        <v>114000</v>
+        <v>29500</v>
       </c>
       <c r="H52" s="3">
-        <v>72400</v>
+        <v>6800</v>
       </c>
       <c r="I52" s="3">
-        <v>73900</v>
+        <v>22200</v>
       </c>
       <c r="J52" s="3">
-        <v>60600</v>
+        <v>900</v>
       </c>
       <c r="K52" s="3"/>
     </row>
@@ -1828,25 +1828,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2684900</v>
+        <v>1976400</v>
       </c>
       <c r="E54" s="3">
-        <v>2866400</v>
+        <v>2110000</v>
       </c>
       <c r="F54" s="3">
-        <v>2886800</v>
+        <v>2125000</v>
       </c>
       <c r="G54" s="3">
-        <v>1681200</v>
+        <v>1237500</v>
       </c>
       <c r="H54" s="3">
-        <v>1396400</v>
+        <v>1013000</v>
       </c>
       <c r="I54" s="3">
-        <v>1258100</v>
+        <v>926100</v>
       </c>
       <c r="J54" s="3">
-        <v>1061600</v>
+        <v>781400</v>
       </c>
       <c r="K54" s="3"/>
     </row>
@@ -1881,25 +1881,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>43300</v>
+        <v>31900</v>
       </c>
       <c r="E57" s="3">
-        <v>55400</v>
+        <v>40800</v>
       </c>
       <c r="F57" s="3">
-        <v>56800</v>
+        <v>41800</v>
       </c>
       <c r="G57" s="3">
-        <v>42500</v>
+        <v>31300</v>
       </c>
       <c r="H57" s="3">
-        <v>32600</v>
+        <v>24000</v>
       </c>
       <c r="I57" s="3">
-        <v>35900</v>
+        <v>26400</v>
       </c>
       <c r="J57" s="3">
-        <v>24800</v>
+        <v>18300</v>
       </c>
       <c r="K57" s="3"/>
     </row>
@@ -1908,25 +1908,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>24700</v>
+        <v>18200</v>
       </c>
       <c r="E58" s="3">
-        <v>19500</v>
+        <v>14400</v>
       </c>
       <c r="F58" s="3">
-        <v>16200</v>
+        <v>12000</v>
       </c>
       <c r="G58" s="3">
-        <v>22200</v>
+        <v>16300</v>
       </c>
       <c r="H58" s="3">
-        <v>11000</v>
+        <v>8100</v>
       </c>
       <c r="I58" s="3">
-        <v>5700</v>
+        <v>4200</v>
       </c>
       <c r="J58" s="3">
-        <v>22600</v>
+        <v>16600</v>
       </c>
       <c r="K58" s="3"/>
     </row>
@@ -1935,25 +1935,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>95200</v>
+        <v>9000</v>
       </c>
       <c r="E59" s="3">
-        <v>152500</v>
+        <v>37900</v>
       </c>
       <c r="F59" s="3">
-        <v>161700</v>
+        <v>52800</v>
       </c>
       <c r="G59" s="3">
-        <v>73400</v>
+        <v>9300</v>
       </c>
       <c r="H59" s="3">
-        <v>54000</v>
+        <v>4600</v>
       </c>
       <c r="I59" s="3">
-        <v>37400</v>
+        <v>3800</v>
       </c>
       <c r="J59" s="3">
-        <v>26500</v>
+        <v>2200</v>
       </c>
       <c r="K59" s="3"/>
     </row>
@@ -1962,25 +1962,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>163200</v>
+        <v>120100</v>
       </c>
       <c r="E60" s="3">
-        <v>227400</v>
+        <v>167400</v>
       </c>
       <c r="F60" s="3">
-        <v>234800</v>
+        <v>172800</v>
       </c>
       <c r="G60" s="3">
-        <v>138100</v>
+        <v>101600</v>
       </c>
       <c r="H60" s="3">
-        <v>97600</v>
+        <v>71900</v>
       </c>
       <c r="I60" s="3">
-        <v>79000</v>
+        <v>58100</v>
       </c>
       <c r="J60" s="3">
-        <v>73900</v>
+        <v>54400</v>
       </c>
       <c r="K60" s="3"/>
     </row>
@@ -1989,25 +1989,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>323700</v>
+        <v>238300</v>
       </c>
       <c r="E61" s="3">
-        <v>317300</v>
+        <v>233600</v>
       </c>
       <c r="F61" s="3">
-        <v>284100</v>
+        <v>209100</v>
       </c>
       <c r="G61" s="3">
-        <v>213200</v>
+        <v>157000</v>
       </c>
       <c r="H61" s="3">
-        <v>230500</v>
+        <v>169700</v>
       </c>
       <c r="I61" s="3">
-        <v>205400</v>
+        <v>151200</v>
       </c>
       <c r="J61" s="3">
-        <v>33200</v>
+        <v>24500</v>
       </c>
       <c r="K61" s="3"/>
     </row>
@@ -2016,25 +2016,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>352900</v>
+        <v>180800</v>
       </c>
       <c r="E62" s="3">
-        <v>404500</v>
+        <v>175300</v>
       </c>
       <c r="F62" s="3">
-        <v>451100</v>
+        <v>181200</v>
       </c>
       <c r="G62" s="3">
-        <v>174800</v>
+        <v>80000</v>
       </c>
       <c r="H62" s="3">
-        <v>168600</v>
+        <v>45200</v>
       </c>
       <c r="I62" s="3">
-        <v>166000</v>
+        <v>31600</v>
       </c>
       <c r="J62" s="3">
-        <v>163200</v>
+        <v>16700</v>
       </c>
       <c r="K62" s="3"/>
     </row>
@@ -2124,25 +2124,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>839900</v>
+        <v>618200</v>
       </c>
       <c r="E66" s="3">
-        <v>949200</v>
+        <v>698700</v>
       </c>
       <c r="F66" s="3">
-        <v>970000</v>
+        <v>714000</v>
       </c>
       <c r="G66" s="3">
-        <v>526100</v>
+        <v>387300</v>
       </c>
       <c r="H66" s="3">
-        <v>496700</v>
+        <v>350600</v>
       </c>
       <c r="I66" s="3">
-        <v>450400</v>
+        <v>331500</v>
       </c>
       <c r="J66" s="3">
-        <v>270300</v>
+        <v>199000</v>
       </c>
       <c r="K66" s="3"/>
     </row>
@@ -2272,25 +2272,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-666400</v>
+        <v>-609900</v>
       </c>
       <c r="E72" s="3">
-        <v>-486300</v>
+        <v>-468900</v>
       </c>
       <c r="F72" s="3">
-        <v>-334700</v>
+        <v>-347800</v>
       </c>
       <c r="G72" s="3">
-        <v>-357900</v>
+        <v>-338900</v>
       </c>
       <c r="H72" s="3">
-        <v>-390600</v>
+        <v>-361600</v>
       </c>
       <c r="I72" s="3">
-        <v>-338800</v>
+        <v>-321100</v>
       </c>
       <c r="J72" s="3">
-        <v>-69500</v>
+        <v>-116500</v>
       </c>
       <c r="K72" s="3"/>
     </row>
@@ -2380,25 +2380,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1845000</v>
+        <v>1358100</v>
       </c>
       <c r="E76" s="3">
-        <v>1917200</v>
+        <v>1411300</v>
       </c>
       <c r="F76" s="3">
-        <v>1916800</v>
+        <v>1411000</v>
       </c>
       <c r="G76" s="3">
-        <v>1155000</v>
+        <v>850200</v>
       </c>
       <c r="H76" s="3">
-        <v>899800</v>
+        <v>662300</v>
       </c>
       <c r="I76" s="3">
-        <v>807700</v>
+        <v>594600</v>
       </c>
       <c r="J76" s="3">
-        <v>791300</v>
+        <v>582500</v>
       </c>
       <c r="K76" s="3"/>
     </row>
@@ -2466,25 +2466,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-183500</v>
+        <v>-135100</v>
       </c>
       <c r="E81" s="3">
-        <v>-155200</v>
+        <v>-114300</v>
       </c>
       <c r="F81" s="3">
-        <v>-6700</v>
+        <v>-4900</v>
       </c>
       <c r="G81" s="3">
-        <v>31400</v>
+        <v>23100</v>
       </c>
       <c r="H81" s="3">
-        <v>-55000</v>
+        <v>-40500</v>
       </c>
       <c r="I81" s="3">
-        <v>-277400</v>
+        <v>-204200</v>
       </c>
       <c r="J81" s="3">
-        <v>-72400</v>
+        <v>-53300</v>
       </c>
       <c r="K81" s="3"/>
     </row>
@@ -2506,25 +2506,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>171400</v>
+        <v>126200</v>
       </c>
       <c r="E83" s="3">
-        <v>186700</v>
+        <v>137400</v>
       </c>
       <c r="F83" s="3">
-        <v>160700</v>
+        <v>118300</v>
       </c>
       <c r="G83" s="3">
-        <v>76500</v>
+        <v>56300</v>
       </c>
       <c r="H83" s="3">
-        <v>91300</v>
+        <v>67200</v>
       </c>
       <c r="I83" s="3">
-        <v>128400</v>
+        <v>94500</v>
       </c>
       <c r="J83" s="3">
-        <v>106100</v>
+        <v>78100</v>
       </c>
       <c r="K83" s="3"/>
     </row>
@@ -2668,25 +2668,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>82600</v>
+        <v>55600</v>
       </c>
       <c r="E89" s="3">
-        <v>18700</v>
+        <v>19000</v>
       </c>
       <c r="F89" s="3">
-        <v>93400</v>
+        <v>68700</v>
       </c>
       <c r="G89" s="3">
-        <v>108300</v>
+        <v>79700</v>
       </c>
       <c r="H89" s="3">
-        <v>190200</v>
+        <v>140000</v>
       </c>
       <c r="I89" s="3">
-        <v>45200</v>
+        <v>33300</v>
       </c>
       <c r="J89" s="3">
-        <v>95700</v>
+        <v>70500</v>
       </c>
       <c r="K89" s="3"/>
     </row>
@@ -2708,25 +2708,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-198300</v>
+        <v>-146000</v>
       </c>
       <c r="E91" s="3">
-        <v>-295700</v>
+        <v>-217700</v>
       </c>
       <c r="F91" s="3">
-        <v>-256700</v>
+        <v>-189000</v>
       </c>
       <c r="G91" s="3">
-        <v>-155500</v>
+        <v>-112000</v>
       </c>
       <c r="H91" s="3">
-        <v>-161100</v>
+        <v>-118600</v>
       </c>
       <c r="I91" s="3">
-        <v>-151200</v>
+        <v>-111300</v>
       </c>
       <c r="J91" s="3">
-        <v>-102600</v>
+        <v>-75500</v>
       </c>
       <c r="K91" s="3"/>
     </row>
@@ -2789,25 +2789,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-209200</v>
+        <v>-154000</v>
       </c>
       <c r="E94" s="3">
-        <v>-290400</v>
+        <v>-213800</v>
       </c>
       <c r="F94" s="3">
-        <v>-245600</v>
+        <v>-180800</v>
       </c>
       <c r="G94" s="3">
-        <v>-172700</v>
+        <v>-127100</v>
       </c>
       <c r="H94" s="3">
-        <v>-158900</v>
+        <v>-116900</v>
       </c>
       <c r="I94" s="3">
-        <v>-159000</v>
+        <v>-117000</v>
       </c>
       <c r="J94" s="3">
-        <v>-103100</v>
+        <v>-75900</v>
       </c>
       <c r="K94" s="3"/>
     </row>
@@ -2829,13 +2829,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8000</v>
+        <v>5900</v>
       </c>
       <c r="E96" s="3">
-        <v>-9300</v>
+        <v>6900</v>
       </c>
       <c r="F96" s="3">
-        <v>-5300</v>
+        <v>3900</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -2937,25 +2937,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>87800</v>
+        <v>64600</v>
       </c>
       <c r="E100" s="3">
-        <v>154700</v>
+        <v>113900</v>
       </c>
       <c r="F100" s="3">
-        <v>151900</v>
+        <v>111800</v>
       </c>
       <c r="G100" s="3">
-        <v>158400</v>
+        <v>116600</v>
       </c>
       <c r="H100" s="3">
-        <v>119100</v>
+        <v>87700</v>
       </c>
       <c r="I100" s="3">
-        <v>34600</v>
+        <v>25400</v>
       </c>
       <c r="J100" s="3">
-        <v>-11800</v>
+        <v>-8700</v>
       </c>
       <c r="K100" s="3"/>
     </row>
@@ -2964,25 +2964,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3600</v>
+        <v>2700</v>
       </c>
       <c r="E101" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="F101" s="3">
-        <v>-600</v>
+        <v>-400</v>
       </c>
       <c r="G101" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H101" s="3">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="I101" s="3">
-        <v>-3800</v>
+        <v>-2800</v>
       </c>
       <c r="J101" s="3">
-        <v>4400</v>
+        <v>3200</v>
       </c>
       <c r="K101" s="3"/>
     </row>
@@ -2991,25 +2991,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-35100</v>
+        <v>-31100</v>
       </c>
       <c r="E102" s="3">
-        <v>-117500</v>
+        <v>-81300</v>
       </c>
       <c r="F102" s="3">
-        <v>-900</v>
+        <v>-700</v>
       </c>
       <c r="G102" s="3">
-        <v>94500</v>
+        <v>69600</v>
       </c>
       <c r="H102" s="3">
-        <v>152100</v>
+        <v>112000</v>
       </c>
       <c r="I102" s="3">
-        <v>-83000</v>
+        <v>-61100</v>
       </c>
       <c r="J102" s="3">
-        <v>-14800</v>
+        <v>-10900</v>
       </c>
       <c r="K102" s="3"/>
     </row>

--- a/AAII_Financials/Yearly/AG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>AG</t>
   </si>
@@ -656,135 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>560600</v>
+      </c>
+      <c r="E8" s="3">
         <v>573800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>624200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>584100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>363900</v>
       </c>
       <c r="H8" s="3">
         <v>363900</v>
       </c>
       <c r="I8" s="3">
+        <v>363900</v>
+      </c>
+      <c r="J8" s="3">
         <v>300900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>252300</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>368400</v>
+      </c>
+      <c r="E9" s="3">
         <v>432100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>483600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>378100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>218800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>236500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>221300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>159300</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>192200</v>
+      </c>
+      <c r="E10" s="3">
         <v>141700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>140600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>206000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>145000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>127500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>79700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>93000</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +808,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -822,9 +835,12 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -849,63 +865,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>61900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>8900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>37800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>60300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>24400</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E15" s="3">
         <v>220200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>135800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>116600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>54400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>89200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>242700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>120700</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -914,62 +939,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>555100</v>
+      </c>
+      <c r="E17" s="3">
         <v>712500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>675800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>537300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>308700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>363300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>494200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>306700</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-138700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-51600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>55200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-193300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-54400</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -981,143 +1013,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-13500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3800</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E21" s="3">
         <v>94900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>81900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>164500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>101900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>93700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>46900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>70100</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E22" s="3">
         <v>15200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2800</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-195900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-61400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>25300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-39000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-263000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-75300</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-60800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>52900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>30200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-58900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-22000</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1142,63 +1190,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-101900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-135100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-114300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-40500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-204200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-53300</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-101900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-135100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-114300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-40500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-204200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-53300</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1223,9 +1280,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1250,9 +1310,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1277,9 +1340,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1304,63 +1370,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E32" s="3">
         <v>13500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3800</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-101900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-135100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-114300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-40500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-204200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-53300</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1385,68 +1460,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-101900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-135100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-114300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-40500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-204200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-53300</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1458,8 +1542,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1471,170 +1556,189 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>202200</v>
+      </c>
+      <c r="E41" s="3">
         <v>125600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>151400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>237900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>238600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>169000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>57000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>118100</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E42" s="3">
         <v>62400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>34500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>36300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11300</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E43" s="3">
         <v>48700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>41200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>54300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>45900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>33900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>66200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20900</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E44" s="3">
         <v>63700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>64800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>60600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>32500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>30500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>32500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18900</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>72700</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2000</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>368800</v>
+      </c>
+      <c r="E46" s="3">
         <v>309100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>370300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>397200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>356000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>243000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>166300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>170700</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1659,36 +1763,42 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1437100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1432400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1539100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1527000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>782300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>712100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>686700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>566200</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1713,9 +1823,12 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1740,9 +1853,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1767,36 +1883,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E52" s="3">
         <v>146200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>143600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>126500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>900</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1821,36 +1943,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1979800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1976400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2110000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2125000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1237500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1013000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>926100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>781400</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1862,8 +1990,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1875,170 +2004,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E57" s="3">
         <v>31900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>40800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18300</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E58" s="3">
         <v>18200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16600</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E59" s="3">
         <v>9000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>37900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>144300</v>
+      </c>
+      <c r="E60" s="3">
         <v>120100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>167400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>172800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>101600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>71900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>58100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>54400</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E61" s="3">
         <v>238300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>233600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>209100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>157000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>169700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>151200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24500</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>184300</v>
+      </c>
+      <c r="E62" s="3">
         <v>180800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>175300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>181200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>80000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>45200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>31600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16700</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2063,9 +2211,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2090,9 +2241,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2117,36 +2271,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>628700</v>
+      </c>
+      <c r="E66" s="3">
         <v>618200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>698700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>714000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>387300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>350600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>331500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>199000</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2158,8 +2318,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2184,9 +2345,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2211,9 +2375,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2238,9 +2405,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2265,36 +2435,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-717100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-609900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-468900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-347800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-338900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-361600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-321100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-116500</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2319,9 +2495,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2346,9 +2525,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2373,36 +2555,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1351100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1358100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1411300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1411000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>850200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>662300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>594600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>582500</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2427,68 +2615,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-101900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-135100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-114300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-40500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-204200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-53300</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2500,35 +2697,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>125500</v>
+      </c>
+      <c r="E83" s="3">
         <v>126200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>137400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>118300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>56300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>67200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>94500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>78100</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2553,9 +2754,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2580,9 +2784,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2607,9 +2814,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2634,9 +2844,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2661,36 +2874,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>152000</v>
+      </c>
+      <c r="E89" s="3">
         <v>55600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>68700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>79700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>140000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>33300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>70500</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2702,35 +2921,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-146000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-217700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-189000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-112000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-118600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-111300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-75500</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2755,9 +2978,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2782,36 +3008,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-114200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-154000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-213800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-180800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-127100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-116900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-117000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-75900</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2823,23 +3055,24 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E96" s="3">
         <v>5900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>6900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3900</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -2849,9 +3082,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2876,9 +3112,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2903,9 +3142,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2930,88 +3172,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E100" s="3">
         <v>64600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>113900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>111800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>116600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>87700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>25400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8700</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E101" s="3">
         <v>2700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3200</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-31100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-81300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>69600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>112000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-61100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10900</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>AG</t>
   </si>
@@ -656,147 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1257200</v>
+      </c>
+      <c r="E8" s="3">
         <v>560600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>573800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>624200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>584100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>363900</v>
       </c>
       <c r="I8" s="3">
         <v>363900</v>
       </c>
       <c r="J8" s="3">
+        <v>363900</v>
+      </c>
+      <c r="K8" s="3">
         <v>300900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>252300</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>563800</v>
+      </c>
+      <c r="E9" s="3">
         <v>368400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>432100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>483600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>378100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>218800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>236500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>221300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>159300</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>693400</v>
+      </c>
+      <c r="E10" s="3">
         <v>192200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>141700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>140600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>206000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>145000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>127500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>79700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>93000</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +821,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,9 +851,12 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,69 +884,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-16400</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>61900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>8900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>37800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>60300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>24400</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>246600</v>
+      </c>
+      <c r="E15" s="3">
         <v>124000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>220200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>135800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>116600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>54400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>89200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>242700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>120700</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -940,68 +965,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>890300</v>
+      </c>
+      <c r="E17" s="3">
         <v>555100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>712500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>675800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>537300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>308700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>363300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>494200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>306700</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>366800</v>
+      </c>
+      <c r="E18" s="3">
         <v>5500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-138700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-51600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>46800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>55200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-193300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-54400</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1014,158 +1046,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>21800</v>
+        <v>-15600</v>
       </c>
       <c r="E20" s="3">
-        <v>-13500</v>
+        <v>18800</v>
       </c>
       <c r="F20" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="G20" s="3">
         <v>2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3800</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>107700</v>
+        <v>629000</v>
       </c>
       <c r="E21" s="3">
-        <v>94900</v>
+        <v>110700</v>
       </c>
       <c r="F21" s="3">
+        <v>97600</v>
+      </c>
+      <c r="G21" s="3">
         <v>81900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>164500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>101900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>93700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>46900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>70100</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>15400</v>
+        <v>18500</v>
       </c>
       <c r="E22" s="3">
-        <v>15200</v>
+        <v>18500</v>
       </c>
       <c r="F22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="G22" s="3">
         <v>12900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2800</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>395000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-26500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-195900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-61400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>25300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>29700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-39000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-263000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-75300</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>184100</v>
+      </c>
+      <c r="E24" s="3">
         <v>75400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-60800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>52900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>30200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-58900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-22000</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1193,69 +1241,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-101900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-135100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-114300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-40500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-204200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-53300</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>164900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-101900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-135100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-114300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>23100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-40500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-204200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-53300</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1283,9 +1340,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1313,9 +1373,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1343,9 +1406,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1373,69 +1439,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-21800</v>
+        <v>15600</v>
       </c>
       <c r="E32" s="3">
-        <v>13500</v>
+        <v>-18800</v>
       </c>
       <c r="F32" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3800</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>164900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-101900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-135100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-114300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>23100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-40500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-204200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-53300</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1463,74 +1538,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>164900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-101900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-135100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-114300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>23100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-40500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-204200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-53300</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1543,8 +1627,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1557,128 +1642,141 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>793400</v>
+      </c>
+      <c r="E41" s="3">
         <v>202200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>125600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>151400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>237900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>238600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>169000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>57000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>118100</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>180400</v>
+      </c>
+      <c r="E42" s="3">
         <v>49800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>62400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>34500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>36300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11300</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E43" s="3">
         <v>46200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>54300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>45900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>33900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>66200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20900</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E44" s="3">
         <v>62500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>63700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>64800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>60600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>30500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>32500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>18900</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1688,57 +1786,63 @@
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>72700</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2000</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1192700</v>
+      </c>
+      <c r="E46" s="3">
         <v>368800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>309100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>370300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>397200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>356000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>243000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>166300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>170700</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1766,39 +1870,45 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3255000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1437100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1432400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1539100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1527000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>782300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>712100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>686700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>566200</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1826,9 +1936,12 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1856,9 +1969,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1886,39 +2002,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>161900</v>
+      </c>
+      <c r="E52" s="3">
         <v>122500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>146200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>143600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>126500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>900</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1946,39 +2068,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4694900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1979800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1976400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2110000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2125000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1237500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1013000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>926100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>781400</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1991,8 +2119,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2005,188 +2134,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E57" s="3">
         <v>35400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>40800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18300</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E58" s="3">
         <v>17000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16600</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>240500</v>
+      </c>
+      <c r="E59" s="3">
         <v>24100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>37900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>52800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>459100</v>
+      </c>
+      <c r="E60" s="3">
         <v>144300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>120100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>167400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>172800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>101600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>71900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>54400</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>297500</v>
+      </c>
+      <c r="E61" s="3">
         <v>220000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>238300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>233600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>209100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>157000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>169700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>151200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24500</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>194400</v>
+      </c>
+      <c r="E62" s="3">
         <v>184300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>180800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>175300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>181200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>80000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>45200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16700</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2214,9 +2362,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2244,9 +2395,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2274,39 +2428,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1521900</v>
+      </c>
+      <c r="E66" s="3">
         <v>628700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>618200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>698700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>714000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>387300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>350600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>331500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>199000</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2319,8 +2479,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2348,9 +2509,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2378,9 +2542,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2408,9 +2575,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2438,39 +2608,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-562000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-717100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-609900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-468900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-347800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-338900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-361600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-321100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-116500</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2498,9 +2674,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2528,9 +2707,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2558,39 +2740,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2761000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1351100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1358100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1411300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1411000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>850200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>662300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>594600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>582500</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2618,74 +2806,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>164900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-101900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-135100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-114300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>23100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-40500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-204200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-53300</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2698,38 +2895,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>264800</v>
+      </c>
+      <c r="E83" s="3">
         <v>125500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>126200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>137400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>118300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>56300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>67200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>94500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>78100</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2757,9 +2958,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2787,9 +2991,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2817,9 +3024,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2847,9 +3057,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2877,39 +3090,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>526000</v>
+      </c>
+      <c r="E89" s="3">
         <v>152000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>55600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>19000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>68700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>79700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>140000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>70500</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2922,38 +3141,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-210700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-115100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-146000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-217700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-189000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-112000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-118600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-111300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-75500</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2981,9 +3204,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3011,39 +3237,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-114200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-154000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-213800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-180800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-127100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-116900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-117000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-75900</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3056,26 +3288,27 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E96" s="3">
         <v>5300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>6900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3900</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -3085,9 +3318,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3115,9 +3351,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3145,9 +3384,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3175,97 +3417,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E100" s="3">
         <v>42400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>64600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>113900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>111800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>116600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>87700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>25400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8700</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3200</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>591300</v>
+      </c>
+      <c r="E102" s="3">
         <v>76600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-31100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-81300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>69600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>112000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-61100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10900</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
